--- a/PRUEBAS A CALIFICAR/Ya procesadas/COLEGIO LAS MARGARITAS-501_Ajustado_20260626_130957.xlsx
+++ b/PRUEBAS A CALIFICAR/Ya procesadas/COLEGIO LAS MARGARITAS-501_Ajustado_20260626_130957.xlsx
@@ -5,22 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Catherine Espinosa\Desktop\Ajustar 3 y 5\Ajustados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Catherine Espinosa\Desktop\PROYECTO JULIANA\PRUEBAS A CALIFICAR\Ya procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_E93E8165D5435E4F6B74DC97565DCE3A97C5004B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955D427F-5C3C-47E8-8C72-25F9EFAB622C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="380" windowWidth="19190" windowHeight="10080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resultados!$A$1:$AB$81</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="118">
   <si>
     <t>Est.</t>
   </si>
@@ -371,6 +374,9 @@
   </si>
   <si>
     <t>1146135169</t>
+  </si>
+  <si>
+    <t>1141349754</t>
   </si>
 </sst>
 </file>
@@ -4232,8 +4238,8 @@
       <c r="D42" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>75</v>
+      <c r="E42" t="s">
+        <v>117</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>32</v>
@@ -4318,8 +4324,8 @@
       <c r="D43" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>75</v>
+      <c r="E43" t="s">
+        <v>117</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>32</v>
@@ -7598,6 +7604,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AB81" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>